--- a/tests/workbooktests/workbooks/extras/test_alias_repository.xlsx
+++ b/tests/workbooktests/workbooks/extras/test_alias_repository.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\extras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\extras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414606B8-6223-4C9B-8197-8E3DC1659073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3649344-8073-4839-9BB4-43CB6D5F81D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74A8DA6A-BC56-4206-BAAB-E5B423CC98C8}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{74A8DA6A-BC56-4206-BAAB-E5B423CC98C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Ibor Leg" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -180,7 +180,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -513,13 +513,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DF8D7F-06F7-4C65-A83C-66B48A78A848}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="68.88671875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -527,7 +527,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -536,7 +536,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -545,7 +545,7 @@
         <v>欣[test_alias_repository.xlsx]Ibor Leg!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -554,7 +554,7 @@
         <v>欣[test_alias_repository.xlsx]Ibor Leg!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -563,7 +563,7 @@
         <v>DISC_CURVE#0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -572,7 +572,7 @@
         <v>PROJ_CURVE#0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -581,7 +581,7 @@
         <v>EURIBOR3M#0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -590,7 +590,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -599,7 +599,7 @@
         <v>46541</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -608,7 +608,7 @@
         <v>SCHEDULE#0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -616,7 +616,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -625,7 +625,7 @@
         <v>SCHEDULE#0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -633,16 +633,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="2" t="str" cm="1">
-        <f t="array" ref="B19">_xll.qlAliasSet("IborLeg",_xll.qlIborLeg(B16,_xll.qlAliasGet(B17),_xll.qlAliasGet(B18),,,,,,,,,,,,,,,,B10))</f>
-        <v>IBORLEG#3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="array" ref="B19">_xll.qlAliasSet("IborLeg",_xll.qlIborLeg(B16,_xll.qlAliasGet(B17),_xll.qlAliasGet(B18),,,,,,,,,,,,,,,,,B10))</f>
+        <v>IBORLEG#0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -651,7 +651,7 @@
         <v>295.49608582322026</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B25" s="6"/>
     </row>
   </sheetData>
@@ -671,19 +671,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54CECCD-0510-486C-9A1F-B00724C98487}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="72.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" customWidth="1"/>
+    <col min="2" max="2" width="72.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:E7">_xll.qlAliasGetRepository('Ibor Leg'!B21)</f>
         <v>ALIAS</v>
@@ -701,9 +701,9 @@
         <v>UPDATED</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
-        <v>DISC_CURVE</v>
+        <v>PROJ_CURVE</v>
       </c>
       <c r="B3" t="str">
         <v>欣[test_alias_repository.xlsx]Dictionary!R2C1YieldTermStructureHandle,A</v>
@@ -712,47 +712,47 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>46310.737994414303</v>
+        <v>46325.384420772338</v>
       </c>
       <c r="E3" s="3">
-        <v>46310.737994414587</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46325.384420772396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
-        <v>PROJ_CURVE</v>
+        <v>EURIBOR3M</v>
       </c>
       <c r="B4" t="str">
-        <v>欣[test_alias_repository.xlsx]Dictionary!R2C1YieldTermStructureHandle,B</v>
+        <v>欣[test_alias_repository.xlsx]Dictionary!R2C1Euribor,A</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" s="3">
-        <v>46310.737994424031</v>
+        <v>46325.384420784503</v>
       </c>
       <c r="E4" s="3">
-        <v>46310.737994424133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46325.384420784605</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
-        <v>EURIBOR3M</v>
+        <v>DISC_CURVE</v>
       </c>
       <c r="B5" t="str">
-        <v>欣[test_alias_repository.xlsx]Dictionary!R2C1Euribor,A</v>
+        <v>欣[test_alias_repository.xlsx]Dictionary!R2C1YieldTermStructureHandle,B</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" s="3">
-        <v>46310.737994447023</v>
+        <v>46325.384420786329</v>
       </c>
       <c r="E5" s="3">
-        <v>46310.737994447249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46325.384420786388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <v>SCHEDULE</v>
       </c>
@@ -763,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="3">
-        <v>46310.737994453055</v>
+        <v>46325.384420795541</v>
       </c>
       <c r="E6" s="3">
-        <v>46310.737994453069</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46325.384420795657</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <v>IBORLEG</v>
       </c>
@@ -777,21 +777,21 @@
         <v>欣[test_alias_repository.xlsx]Dictionary!R2C1numpy.ndarray,A</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3">
-        <v>46310.73799447537</v>
+        <v>46325.384420818613</v>
       </c>
       <c r="E7" s="3">
-        <v>46310.738516821999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46325.384420818649</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="str" cm="1">
         <f t="array" ref="A11:B15">_xll.qlAliasEnvelope(A6,A2)</f>
         <v>ALIAS</v>
@@ -800,7 +800,7 @@
         <v>SCHEDULE</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <v>OBJECT</v>
       </c>
@@ -808,7 +808,7 @@
         <v>欣[test_alias_repository.xlsx]Dictionary!R11C1Schedule,A</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <v>VERSION</v>
       </c>
@@ -816,20 +816,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <v>CREATED</v>
       </c>
       <c r="B14" s="3">
-        <v>46310.737994453055</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46325.384420795541</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <v>UPDATED</v>
       </c>
       <c r="B15" s="3">
-        <v>46310.737994453069</v>
+        <v>46325.384420795657</v>
       </c>
     </row>
   </sheetData>
